--- a/RadCluster_2_0/input/input_parameters.xlsx
+++ b/RadCluster_2_0/input/input_parameters.xlsx
@@ -3086,7 +3086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -3808,6 +3808,238 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Loop 1/2&lt;111&gt; -&gt; &lt;100&gt; Conversion (Marian 2002 + Dudarev 2008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unary barrier offset</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>E_a0_conv</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>eV</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Dudarev unary E_a^0; Marian dH2 ~ 1.0 eV</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unary barrier size slope</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>gamma_a_conv</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>eV</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>per perimeter-segment; calibrate to Arakawa onset</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unary attempt frequency</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>nu0_conv</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>10000000000000</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1/s</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Debye</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Conversion crossover temp</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>T_star_conv_C</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>450</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>dF(n_ref,T*)=0; in [350,550] (Dudarev Fig.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Conversion reference size</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>n_ref_conv</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>50</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>calibration anchor size for LoopEnergetics</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Junction peak yield</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>phi_max_junc</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Marian; yield at n=n_prime (0-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Junction log-size tol.</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>sigma_s_junc</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Marian comparable-size width in ln(n/np)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Junction min size</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>n_j_min_junc</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>30</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Marian; junctions from n ~ 34-37</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>&lt;100&gt; loop-onset size</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>n_loop_min</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>bulk-100 n_min; below this no &lt;100&gt; loop</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RadCluster_2_0/input/input_parameters.xlsx
+++ b/RadCluster_2_0/input/input_parameters.xlsx
@@ -3086,7 +3086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="31.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4037,6 +4037,56 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>bulk-100 n_min; below this no &lt;100&gt; loop</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Two-step barrier</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>dH2_conv</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>eV</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Marian Fig.3 1/2&lt;110&gt;-&gt;&lt;100&gt; fwd</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Two-step barrier</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>dH_rev_conv</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>eV</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Marian Fig.3 1/2&lt;110&gt;-&gt;1/2&lt;111&gt; rev</t>
         </is>
       </c>
     </row>

--- a/RadCluster_2_0/input/input_parameters.xlsx
+++ b/RadCluster_2_0/input/input_parameters.xlsx
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/RadCluster_2_0/input/input_parameters.xlsx
+++ b/RadCluster_2_0/input/input_parameters.xlsx
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
